--- a/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno1/anno1_task4_overall_dial.xlsx
+++ b/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno1/anno1_task4_overall_dial.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87EC8C10-1CD7-4047-8D22-F886560D2F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Projects\RLHF\phases\phase2\hh-annotations\results\kallirroi\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5725ACE9-DFBB-4EC8-A18B-1366DBAA218A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="900" windowWidth="41080" windowHeight="25660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -56,46 +61,46 @@
     <t>COMMENTS</t>
   </si>
   <si>
-    <t>SFTANNO-000132-0004</t>
-  </si>
-  <si>
-    <t>I'm considering an adventure trip to Patagonia.</t>
-  </si>
-  <si>
-    <t>That sounds like an amazing experience! Patagonia's natural wonders are breathtaking. I'm surprised you're thinking of going there.Have you researched the logistics of the trip?</t>
-  </si>
-  <si>
-    <t>Patagonia sounds like an incredible adventure! That's a surprising and exciting choice! Patagonia offers breathtaking landscapes.Have you looked into tour operators for the trip?</t>
-  </si>
-  <si>
-    <t>That sounds like an incredible adventure! Patagonia is a dream destination for many, and I'm excited for you!Have you planned the details of your trip?</t>
-  </si>
-  <si>
-    <t>Patagonia is a breathtaking destination! It's awe-inspiring, but remember to prepare well for such an adventure.Have you started planning for the trip?</t>
-  </si>
-  <si>
-    <t>That's an exciting choice! Patagonia is a unique destination with breathtaking landscapes. I'm surprised you're going there!Have you started planning your Patagonia adventure?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000107-0004</t>
-  </si>
-  <si>
-    <t>It's so cloudy out, I don't even want to leave my house.</t>
-  </si>
-  <si>
-    <t>I hear you, sometimes it feels like there's no end in sight. Did you know that rain can actually be good for your mood? It's been proven to increase the production of serotonin in your brain.Do you have any favorite movies you like to watch on a rainy day?</t>
-  </si>
-  <si>
-    <t>I feel the same way, it's hard to be motivated when it's so gloomy. Have you tried going for a walk in the rain? It can be really refreshing!Do you have any upcoming plans for the weekend?</t>
-  </si>
-  <si>
-    <t>I get it, the clouds can be so depressing sometimes. I'm surprised you're feeling so down, you're usually so optimistic!Do you have any fun plans coming up?</t>
-  </si>
-  <si>
-    <t>I feel the same way, it's so hard to motivate myself when it's this dark outside. Have you ever tried going for a walk in the rain? It can be really peaceful.What's your favorite movie?</t>
-  </si>
-  <si>
-    <t>I know, it can be really discouraging to want to stay inside. Did you know that some people find cloudy days calming and peaceful?Have you tried any new restaurants lately?</t>
+    <t>SFTANNO-000077-0004</t>
+  </si>
+  <si>
+    <t>I didn't know there were so many different regions and cultures in Japan.</t>
+  </si>
+  <si>
+    <t>Yes, it's a diverse country with many different regions and cultures. It's definitely worth exploring different parts of the country and immersing yourself in the local culture.Have you researched which regions you want to visit?</t>
+  </si>
+  <si>
+    <t>It's true, each region has its own unique culture and customs. That's why it's so fascinating to explore.Have you considered visiting different regions during your trip?</t>
+  </si>
+  <si>
+    <t>Yes, Japan is incredibly diverse and there's so much to discover. It's definitely a country that has a lot to offer.Have you looked into any specific regions or cities you want to visit?</t>
+  </si>
+  <si>
+    <t>Yes, it's a diverse country with many different customs and traditions. It's interesting to learn about the different regions and how they each have their own unique culture.Which regions are you planning to visit?</t>
+  </si>
+  <si>
+    <t>Yes, it's a very diverse country. You should try to visit as many different regions as possible to get a full experience of Japan.Do you have any specific places you want to visit in Japan?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000153-0004</t>
+  </si>
+  <si>
+    <t>I'm worried my scrapbook won't be as good as some of the ones I've seen online.</t>
+  </si>
+  <si>
+    <t>I understand, it's natural to compare yourself to others. Your scrapbook will be unique and special to you, no one else's will be exactly like yours.Have you considered adding your own personal touch to the design?</t>
+  </si>
+  <si>
+    <t>It's natural to compare yourself to others, but remember that scrapbooking is a personal and unique art form. I'm surprised you feel that way. Your scrapbook is going to be amazing, no matter what others have done.What kind of materials or embellishments are you planning on using?</t>
+  </si>
+  <si>
+    <t>It's normal to feel that way, but remember, scrapbooking is about capturing your memories, not about being perfect. I'm surprised you're worried about that, but remember, your scrapbook is about your memories and your unique style.Have you considered any unique embellishments or materials you could add?</t>
+  </si>
+  <si>
+    <t>It's natural to compare your work to others, but remember, it's your unique style that makes it special. That's a really insightful perspective. I never thought about it that way before.Have you thought about what type of scrapbooking supplies you want to use?</t>
+  </si>
+  <si>
+    <t>It's normal to feel that way, but remember that scrapbooking is about the memories and the process, not just the end result. It's amazing how scrapbooking has evolved over the years, from a simple way to preserve memories to a creative outlet for so many people.What's your favorite memory from last summer that you're hoping to include in your scrapbook?</t>
   </si>
   <si>
     <t>SFTANNO-000019-0004</t>
@@ -161,46 +166,46 @@
     <t>That's so sad to hear. It's like they don't care about the most vulnerable. It's heartbreaking to think about how many people will be affected by this.Do you think there's anything we can do to help those affected?</t>
   </si>
   <si>
-    <t>SFTANNO-000094-0004</t>
-  </si>
-  <si>
-    <t>Actually, I always opt for middle seats. Fewer distractions around me.</t>
-  </si>
-  <si>
-    <t>I never thought about that before. I can't imagine sitting in the middle seat, it just sounds uncomfortable.Do you have any tips for avoiding jet lag?</t>
-  </si>
-  <si>
-    <t>Really? I can't imagine sitting in the middle seat. The middle seat is the worst; you're stuck in the middle of everything and can't even stretch out.Do you have any travel hacks or tips you like to use?</t>
-  </si>
-  <si>
-    <t>Really? I've never tried that before. That's interesting, but I'm not sure I could handle sitting in the middle with people on either side of me.Have you ever met someone interesting on a flight?</t>
-  </si>
-  <si>
-    <t>Really? I could never imagine choosing a middle seat. I can't believe you choose the middle seat. I would never want to be stuck in the middle.What's your favorite travel destination?</t>
-  </si>
-  <si>
-    <t>That's a unique choice! I'm surprised that you prefer middle seats; I always find them cramped and uncomfortable.Do you have any travel hacks or tips?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000103-0004</t>
-  </si>
-  <si>
-    <t>I've been browsing, but I don't want to compromise on quality either.</t>
-  </si>
-  <si>
-    <t>That's a tricky balance to find. It's tough when you can't find the right fit, but keep looking and don't settle for less.Do you have any favorite VR games or experiences?</t>
-  </si>
-  <si>
-    <t>It's important to find the right fit. It's a tough balance between finding something within budget and not sacrificing quality.Have you considered waiting for a sale or promotion on the VR headset you want?</t>
-  </si>
-  <si>
-    <t>That's a good point, you should only invest in something that meets your standards. It's important to prioritize quality, especially for something like a VR headset.Have you considered saving up or waiting for sales?</t>
-  </si>
-  <si>
-    <t>It's important to find the right balance between quality and price. It's tough to find the right balance, but I'm sure you'll find something that works for you.Have you considered waiting for a sale or discount?</t>
-  </si>
-  <si>
-    <t>It's important to find a balance between quality and affordability. It's tough when we want to invest in new technology, but have to be mindful of our budget.Have you considered any other alternatives or options?</t>
+    <t>SFTANNO-000131-0004</t>
+  </si>
+  <si>
+    <t>I've always dreamed of visiting Japan, but I'm afraid of the language barrier.</t>
+  </si>
+  <si>
+    <t>I can understand your concern. However, many people in Japan speak English, and there are language learning apps available.Have you considered learning some basic Japanese phrases?</t>
+  </si>
+  <si>
+    <t>I can understand the apprehension. But, language barriers can be overcome with language learning apps and local guides. It's an exciting opportunity!Have you looked into any cultural exchange programs?</t>
+  </si>
+  <si>
+    <t>Japan is a fascinating country, but language can be a challenge. You might consider taking a language course or downloading a translation app to ease communication.Any other destinations you're interested in?</t>
+  </si>
+  <si>
+    <t>It's a unique and fascinating country. Don't worry about the language barrier; many people speak English. It'll be an incredible experience.Have you started planning your itinerary?</t>
+  </si>
+  <si>
+    <t>Japan is a beautiful country. You'd be surprised how many English speakers there are. Plus, it's a great opportunity to learn a new language!Have you researched any cultural experiences you'd like to have?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000058-0004</t>
+  </si>
+  <si>
+    <t>I heard a rumor that the COVID-19 vaccine makes you infertile, is that true?</t>
+  </si>
+  <si>
+    <t>No, that's a false claim, and it's been debunked by scientists. But it's important to stay informed and not spread unfounded rumors.How can we help people separate fact from fiction?</t>
+  </si>
+  <si>
+    <t>That's a myth that has been debunked by experts. It's important to rely on scientific evidence and not spread false information.Where did you hear that rumor?</t>
+  </si>
+  <si>
+    <t>No, that's a myth with no scientific basis. The vaccine is safe for all adults. It's important to rely on credible sources for information to avoid spreading misinformation.Do you have any other questions about the vaccine?</t>
+  </si>
+  <si>
+    <t>No, that's a myth. The vaccine doesn't affect fertility in any way. It's scary how easily false information spreads, and it's crucial to correct it.Do you have any tips on how to combat misinformation?</t>
+  </si>
+  <si>
+    <t>No, that's not true. The vaccine has gone through extensive testing and has been proven safe. It's scary how easily misinformation can spread and cause people to be afraid of getting vaccinated.Have you considered getting vaccinated?</t>
   </si>
   <si>
     <t>SFTANNO-000025-0004</t>
@@ -224,151 +229,151 @@
     <t>That's a great idea. I'm surprised at how much better you're feeling about the situation.Do you have any other concerns or questions?</t>
   </si>
   <si>
-    <t>SFTANNO-000064-0004</t>
-  </si>
-  <si>
-    <t>I think we should reach out to local organizations and get involved in promoting change.</t>
-  </si>
-  <si>
-    <t>That's a great idea, it's important to use our voices and make our presence known. It's unacceptable that these issues are still going unchecked. It's time for us to be proactive and show our advocates for our beliefs.What local organizations do you know of that are promoting change?</t>
-  </si>
-  <si>
-    <t>That's a great idea. We can work together to make a positive impact. It's unacceptable that we still have to fight for basic rights and equality. It's time to take action and create change.What local organizations do you recommend we reach out to?</t>
-  </si>
-  <si>
-    <t>That's a great idea, it's important to support local initiatives. It's unacceptable that some people still see certain issues as acceptable. We need to keep pushing for change until we get the results we want.What local organizations do you think we should start with?</t>
-  </si>
-  <si>
-    <t>That's a great idea, we can work together to create a positive impact. It's frustrating that certain issues still persist, but we can work together to create change and make a difference.What organizations do you suggest we reach out to?</t>
-  </si>
-  <si>
-    <t>That's a great idea. We can also use social media to spread awareness and encourage others to take action. It's unacceptable that certain issues are still being overlooked and not given the attention they deserve. We need to be more vocal and take action to create change.How do you suggest we use social media to spread awareness?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000145-0004</t>
-  </si>
-  <si>
-    <t>That's a great idea! I hadn't thought about that.</t>
-  </si>
-  <si>
-    <t>I'm so glad I could help! Let's make a difference together. Yes, let's work together to make a positive impact on our planet!Do you have any other ideas for making sustainable changes?</t>
-  </si>
-  <si>
-    <t>I'm glad I could help! Every little bit helps! That's the spirit! Keep up the great work and we can make a difference together.What other sustainability changes are you thinking about making?</t>
-  </si>
-  <si>
-    <t>It's a great way to learn from others and get support. I'm so happy to hear that! It's so important to find resources and support for making these changes.What other changes do you want to make in your daily life?</t>
-  </si>
-  <si>
-    <t>I'm glad I could help! There are so many ways to get involved and make a difference. It's so inspiring to see people taking action and making a positive impact. Keep up the great work!Do you have any other sustainability tips or ideas you'd like to share?</t>
-  </si>
-  <si>
-    <t>It's always good to have a support system when making changes towards sustainability. It's great to see you taking steps towards sustainability! I'm excited to see what changes you'll make next.Have you considered supporting sustainable fashion brands?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000152-0004</t>
-  </si>
-  <si>
-    <t>I'm worried I won't be able to make anything as beautiful as the examples I've seen.</t>
-  </si>
-  <si>
-    <t>It's normal to feel that way, but don't worry, it takes practice. It's frustrating that the scrapbooking industry can be so competitive and cutthroat.Have you considered taking a class to get some hands-on experience?</t>
-  </si>
-  <si>
-    <t>I understand, but remember that everyone starts somewhere. It's ridiculous that some people expect perfection right away.What kind of project are you thinking about making?</t>
-  </si>
-  <si>
-    <t>It's normal to feel that way, but it's important to remember that it's about the memories, not the aesthetic. It's frustrating that the industry can make it seem like only perfection is acceptable.Have you thought about starting with a simple design and building from there?</t>
-  </si>
-  <si>
-    <t>It's normal to feel that way, but you'll get the hang of it. It's ridiculous that people can be so judgmental and critical.Have you thought about taking a class to learn some techniques?</t>
-  </si>
-  <si>
-    <t>I understand how you feel, but remember, it's all about practice. It's infuriating how much pressure society puts on people to create perfect crafts.What kind of scrapbooking materials do you like to use?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000159-0004</t>
-  </si>
-  <si>
-    <t>We should start by setting some ground rules for respectful discussion.</t>
-  </si>
-  <si>
-    <t>That's a great idea, we can work on that. I'm happy we're taking this step towards better communication.How do we create these rules?</t>
-  </si>
-  <si>
-    <t>Agreed, we need boundaries to prevent future conflicts. I'm happy we can start fresh with clear boundaries.How can we ensure we follow these rules?</t>
-  </si>
-  <si>
-    <t>Agreed, we need to establish boundaries. I'm happy we're taking steps towards a healthier conversation.What rules do you suggest?</t>
-  </si>
-  <si>
-    <t>I agree, we need to show each other respect. I'm happy we're taking steps towards a better conversation.What rules do you suggest we implement?</t>
-  </si>
-  <si>
-    <t>Agreed, let's make sure we listen and respect each other's opinions. I'm happy we're working towards a healthier conversation.What other steps can we take?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000096-0004</t>
-  </si>
-  <si>
-    <t>I missed the last train, and I'm stuck in the city.</t>
-  </si>
-  <si>
-    <t>Oh no, that's really inconvenient. I'm sorry you're stuck here alone. Do you need help getting a ride or anything?Is there anything I can do to help you?</t>
-  </si>
-  <si>
-    <t>Oh no, that's a scary situation. I'm sorry you're in that position. Is there a hotel nearby that you could stay at for the night?I'll help you find one if you need it.</t>
-  </si>
-  <si>
-    <t>Oh no, that's awful. Are you okay? I'm so sorry, it's a terrible feeling being stranded like that.Do you need help finding a nearby hotel or shelter?</t>
-  </si>
-  <si>
-    <t>That's really scary, especially in an unfamiliar place. It's tough to be in that situation, but we can help you find a safe place to stay.Do you have any friends or contacts in the area?</t>
-  </si>
-  <si>
-    <t>That's scary, are you okay? It's tough when things like this happen, but we'll figure it out.Can I help you find a taxi or other transportation option?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000089-0004</t>
-  </si>
-  <si>
-    <t>They have a really solid defense and excellent ball control.</t>
-  </si>
-  <si>
-    <t>Yeah, but they can be quite predictable at times. It's too bad when a team's strengths can also be their downfall.Do you have a favorite soccer player?</t>
-  </si>
-  <si>
-    <t>Yeah, they're hard to beat. It's too bad that not everyone has the same opportunities to play or even watch soccer.Do you have any upcoming soccer games you're looking forward to?</t>
-  </si>
-  <si>
-    <t>It's impressive to see a team that good. It's hard to watch a team like that and not feel sad about your own team's performance.Do you have any other teams you like to watch?</t>
-  </si>
-  <si>
-    <t>I agree, but sometimes their offense can be too predictable. It's too bad that some teams can't seem to compete with them, it's not very exciting.Who do you think is the best player on FC Barcelona?</t>
-  </si>
-  <si>
-    <t>Yeah, they're really good. It's a shame they don't have as much support as other teams, they deserve more recognition.Have you ever been to a live soccer game?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000135-0004</t>
-  </si>
-  <si>
-    <t>I did a river rafting trip once, but the water was so dirty.</t>
-  </si>
-  <si>
-    <t>I can understand why that would be unpleasant. River rafting can be a thrilling adventure, but make sure you choose a reputable company and do your research beforehand.Have you tried any other outdoor adventures?</t>
-  </si>
-  <si>
-    <t>That sounds awful, I hate the idea of rafting in dirty water. It's important to prioritize safety and cleanliness when it comes to adventure activities.Have you ever tried whitewater rafting in a clean river?</t>
-  </si>
-  <si>
-    <t>That's not ideal, but there are plenty of other adventures to choose from. I can understand why you wouldn't want to raft in dirty water.Have you ever tried any adventure sports that involve water?</t>
-  </si>
-  <si>
-    <t>That sounds awful, I couldn't imagine rafting in dirty water. It's important to do your research and choose a reputable company that takes safety and cleanliness seriously.Have you gone rafting on a cleaner river since then?</t>
-  </si>
-  <si>
-    <t>That sounds gross. It's important to do research on the cleanliness of the river and the safety of the rafting company.Have you ever gone on a clean and safe river rafting trip?</t>
+    <t>SFTANNO-000098-0004</t>
+  </si>
+  <si>
+    <t>Have you ever ridden in an autonomous vehicle before?</t>
+  </si>
+  <si>
+    <t>No, I haven't had the chance yet. Really? I'm surprised you haven't tried it yet. It's a unique experience.Do you think you would be interested in taking a ride in one sometime?</t>
+  </si>
+  <si>
+    <t>No, but I'm curious to try it out sometime. Really? I'm surprised to hear that. They're becoming increasingly popular.Would you be open to trying it out sometime?</t>
+  </si>
+  <si>
+    <t>Yes, I have. It was a really smooth ride. I was surprised at how quiet and smooth the ride was. It felt like I was in a limousine.Have you ever tried any other autonomous technologies, like self-driving cars?</t>
+  </si>
+  <si>
+    <t>No, I haven't had the chance to yet. Really? I'm surprised to hear that. Have you considered trying it out?What do you think it would be like to ride in an autonomous vehicle?</t>
+  </si>
+  <si>
+    <t>No, I haven't. Really? I'm surprised to hear that, as they are becoming more and more common.Would you be interested in trying one out?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000050-0004</t>
+  </si>
+  <si>
+    <t>I'm open to anything at this point.</t>
+  </si>
+  <si>
+    <t>That's great! It's hard to be too optimistic when you don't know what to expect.Have you thought about any specific companies you'd like to work for?</t>
+  </si>
+  <si>
+    <t>That's a good attitude to have. I'm here for you if you need anything.Have you thought about reaching out to any recruiters?</t>
+  </si>
+  <si>
+    <t>That's the right attitude. It's tough not knowing what's next, but you'll find something amazing.Have you thought about reaching out to any old colleagues or contacts for job leads?</t>
+  </si>
+  <si>
+    <t>That's a great attitude to have. I'm sorry you're going through this. It's a tough time.Have you looked into any job boards or websites?</t>
+  </si>
+  <si>
+    <t>That's the spirit! It's tough to start over, but I'm here to support you through it.Have you thought about reaching out to any recruiters?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000078-0004</t>
+  </si>
+  <si>
+    <t>I'm worried about cultural misunderstandings when I visit my parents' homeland.</t>
+  </si>
+  <si>
+    <t>It's natural to have concerns about cultural differences, but they can also lead to rich experiences and learning. Have you tried learning some basic phrases or customs beforehand to avoid any misunderstandings?That's a great idea! What phrases or customs have you looked into so far?</t>
+  </si>
+  <si>
+    <t>It's natural to worry about cultural differences, but with some research and preparation, you can have a great experience. Just remember to be open-minded and willing to learn about the culture and customs of the place you're visiting.Have you looked into any cultural exchange programs or language courses that could help you better understand the local culture?</t>
+  </si>
+  <si>
+    <t>That's a valid concern, but it's important to remember that cultural differences are a natural part of any travel experience. I'm surprised to hear that you're worried about cultural misunderstandings. What specific cultural differences are you concerned about?Have you researched any cultural etiquette or customs that you should be aware of before your trip?</t>
+  </si>
+  <si>
+    <t>It's normal to have those concerns, but remember that everyone is different and that cultural differences can be enriching. I'm surprised by your fear, but remember that cultural exchange can lead to a more open-minded and enriching experience.Have you looked into any language courses or resources to help with communication while traveling?</t>
+  </si>
+  <si>
+    <t>It's natural to have concerns, but with proper research and an open mind, you can have a positive experience. It's amazing how much you can learn about your culture by immersing yourself in it.What are some specific things you're looking forward to experiencing in your parents' homeland?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000095-0004</t>
+  </si>
+  <si>
+    <t>Yes, I have. I was so frustrated that the seat was uncomfortable and the entertainment system was broken.</t>
+  </si>
+  <si>
+    <t>That's terrible. I hate when that happens. I can't even imagine how frustrating that must have been. Just make sure you're well-rested before your next long-haul flight.Do you have any tips for avoiding jet lag?</t>
+  </si>
+  <si>
+    <t>Ugh, I hate when that happens. It can really ruin the experience. It's really scary when the entertainment system is broken, and you have nothing to do for hours on end.Have you ever tried any in-flight movies that you really enjoyed?</t>
+  </si>
+  <si>
+    <t>That's terrible! I hate when the entertainment system isn't working. It's so scary when the entertainment system isn't working. It makes the flight feel so much longer.Have you ever flown with a layover?</t>
+  </si>
+  <si>
+    <t>That sounds terrible. It's unacceptable when airlines don't prioritize customer satisfaction. It's scary to think that airlines might not prioritize customer satisfaction, and it could lead to more accidents or incidents.Do you have any tips for surviving long-haul flights?</t>
+  </si>
+  <si>
+    <t>That's so annoying! I've had similar experiences. It's always scary when the entertainment system is broken, and you're stuck in a cramped seat for hours.Do you prefer window or aisle seats?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000139-0004</t>
+  </si>
+  <si>
+    <t>I'm scared my children are spending too much time online.</t>
+  </si>
+  <si>
+    <t>It's important to monitor their online activity and set boundaries. It's really important to keep an eye on their online activity and make sure they're not being exposed to anything inappropriate.Have you talked to your children about online safety?</t>
+  </si>
+  <si>
+    <t>It's a valid concern, there are so many risks. It's disgusting how much content online can be harmful to children.Have you talked to them about online safety?</t>
+  </si>
+  <si>
+    <t>It's a valid concern, especially with all the dangers online. It's disgusting that there are so many dangers online for kids to encounter.Have you talked to your kids about online safety and how to avoid dangers?</t>
+  </si>
+  <si>
+    <t>It's a valid concern, especially with all the content out there. It's so important to monitor their online activity and ensure they're safe.Have you considered setting up parental controls or online monitoring software?</t>
+  </si>
+  <si>
+    <t>It's important to monitor their online activity. It's so disgusting that there are predators lurking online.Have you talked to your children about online safety?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000130-0004</t>
+  </si>
+  <si>
+    <t>One episode covered the injustices faced by indigenous communities in regard to traditional plant knowledge and genetics research.</t>
+  </si>
+  <si>
+    <t>That's a frustrating and complicated issue. It's great that there are more resources and platforms for discussing these important issues.Have you found any other resources that cover the intersection of plant genetics and social justice?</t>
+  </si>
+  <si>
+    <t>That's a really important issue that needs to be addressed. It's great that the podcast is covering these important issues and bringing awareness to the need for more ethical and inclusive research practices.Do you have any recommendations for other podcasts or resources that cover similar topics?</t>
+  </si>
+  <si>
+    <t>That's a terrible situation. It's heartening to see researchers acknowledging the importance of indigenous perspectives and working towards more inclusive research practices.What do you think can be done to improve the representation of indigenous voices in plant genetics research?</t>
+  </si>
+  <si>
+    <t>That's upsetting to hear. It's important to raise awareness about these issues and work towards ethical and equitable practices in plant genetics research.Do you know of any organizations that are working towards these goals?</t>
+  </si>
+  <si>
+    <t>That's a serious issue that needs to be addressed. It's important to acknowledge and address these injustices, and I'm glad that the podcast is bringing attention to this issue.What other topics do you think the podcast should cover?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000073-0004</t>
+  </si>
+  <si>
+    <t>I saw a video of a robot dancing and it was just strange to watch.</t>
+  </si>
+  <si>
+    <t>I agree, it's not really human-like movement. It's a bit unsettling to think about the idea of robots being able to mimic human movement so closely.Do you think robots will ever be able to perfectly replicate human movement?</t>
+  </si>
+  <si>
+    <t>I can imagine. Robots are just not meant to dance. I agree, and the thought of robots taking over other areas of our lives that we enjoy, like dancing, is really scary.What other areas of our lives do you think robots could potentially take over?</t>
+  </si>
+  <si>
+    <t>I can imagine. It's almost like they're taking away the uniqueness of human dance. I'm worried that if robots can replicate human movements, it could lead to a loss of individuality in art forms.Do you think robots could ever replicate the emotional connection we have with dance?</t>
+  </si>
+  <si>
+    <t>I agree, it's kind of unsettling to see robots mimicking human behavior. It's a bit scary to think about how much robots are capable of these days.Do you think there should be regulations put in place for robots and their capabilities?</t>
+  </si>
+  <si>
+    <t>I can imagine. It's not something I'd want to watch either. I can't imagine what kind of damage a robot could do if it malfunctions during a dance routine.Have you ever interacted with a robot before?</t>
   </si>
   <si>
     <t>SFTANNO-000018-0004</t>
@@ -392,46 +397,46 @@
     <t>It is incredible, isn't it? Yes, it's fascinating how much we're learning about the universe. It's so exciting!Have you ever thought about studying astronomy?</t>
   </si>
   <si>
-    <t>SFTANNO-000163-0004</t>
-  </si>
-  <si>
-    <t>I wish I could go back in time to see history up close.</t>
-  </si>
-  <si>
-    <t>It's sad that we can't go back and witness history firsthand. It's a common feeling, but we should be grateful for the ability to learn about history through books and documentaries.What historical event would you like to witness if you could?</t>
-  </si>
-  <si>
-    <t>I understand the desire to experience history firsthand. While I understand your longing, it's essential to remember that time travel is just a fantasy.Have you ever visited any historical sites?</t>
-  </si>
-  <si>
-    <t>I understand your sentiment, but it's important to respect the timeline. We can learn a lot about history through books and documentaries.Have you ever read a book about a historical event?</t>
-  </si>
-  <si>
-    <t>It's a bittersweet feeling, wanting to experience history firsthand. We can always learn about history through research and study.It's important to appreciate history as it is, not just wish we could change it.</t>
-  </si>
-  <si>
-    <t>I know what you mean, it would be amazing to witness some of the most important events in history. Maybe there's a way to experience history without time travel, like visiting museums or historical sites.It's always important to appreciate and learn from the past.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000102-0004</t>
-  </si>
-  <si>
-    <t>The new Pokemon game is such a cash grab. They're releasing the same version with only minor updates.</t>
-  </si>
-  <si>
-    <t>I can't believe they're taking advantage of their fans like that. It's infuriating, they should be focusing on making better games.Have you tried playing any other Pokemon games in the meantime?</t>
-  </si>
-  <si>
-    <t>I know, it's so frustrating. It feels like they're not even trying anymore.Have you tried playing any of the older Pokemon games?</t>
-  </si>
-  <si>
-    <t>I completely agree, it's a money-making scheme. They're exploiting their loyal fanbase, it's maddening.What other games have you been playing lately?</t>
-  </si>
-  <si>
-    <t>I completely understand your frustration. It's frustrating when companies rely on their brand instead of innovation.Have you considered trying a different game instead?</t>
-  </si>
-  <si>
-    <t>It's so frustrating when they do that. It's just a ploy to make more money, it's not fair to the fans.What other Pokemon games have you played?</t>
+    <t>SFTANNO-000105-0004</t>
+  </si>
+  <si>
+    <t>I don't like this cold and gloomy weather.</t>
+  </si>
+  <si>
+    <t>I completely understand, it's so depressing. It's understandable to feel that way. I hope it gets better soon.Have you tried any indoor activities to lift your spirits?</t>
+  </si>
+  <si>
+    <t>I know, it's so depressing. I hope it gets warmer soon. Have you tried any cozy indoor activities?What's your favorite thing to do on a cold day?</t>
+  </si>
+  <si>
+    <t>I know, it's really depressing. It's hard to find the motivation to do anything when it's so cold outside.Have you tried any new indoor activities recently?</t>
+  </si>
+  <si>
+    <t>Me neither, it makes me feel so unmotivated. Maybe we should plan a fun indoor activity to lift our spirits.Have you ever tried indoor rock climbing?</t>
+  </si>
+  <si>
+    <t>I know, it's hard to stay motivated in this weather. Have you tried any indoor activities to lift your spirits?What's your favorite way to spend a rainy day?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000154-0004</t>
+  </si>
+  <si>
+    <t>My partner keeps criticizing how I chop vegetables, it's driving me insane.</t>
+  </si>
+  <si>
+    <t>Ugh, I hate when people criticize our cooking methods. Just remember that everyone has their own style and technique, and it's okay if it's not the same as someone else's.Have you tried watching cooking shows or reading recipes together to find a compromise?</t>
+  </si>
+  <si>
+    <t>That's so frustrating, they should be more supportive. Maybe you could suggest taking a cooking class together, or practicing together at home. It's important that you feel comfortable and confident in the kitchen.Have you thought about trying a new recipe together?</t>
+  </si>
+  <si>
+    <t>That's so frustrating, it's not your fault if they can't cut their own veggies. Maybe try explaining to them how it's not constructive criticism and it's affecting your cooking experience.Do you have any other cooking tips to share?</t>
+  </si>
+  <si>
+    <t>That's so frustrating, everyone has their own way of doing things. Maybe try to explain to them that there isn't a right or wrong way to chop vegetables, as long as they're safe to eat and easy to cook with.Have you tried talking to them about it?</t>
+  </si>
+  <si>
+    <t>That's frustrating, they should trust your skills in the kitchen. Maybe try having a conversation with them about it and explain that you have your own way of doing things.Have you tried any new recipes lately?</t>
   </si>
   <si>
     <t>SFTANNO-000011-0004</t>
@@ -476,32 +481,32 @@
     <t>It's such a difficult balance. It's not fair that we have to worry about the cost of something that should be about celebrating love.Have you considered borrowing a dress from a friend or family member?</t>
   </si>
   <si>
-    <t>SFTANNO-000062-0004</t>
-  </si>
-  <si>
-    <t>I'm thrilled to see more young people engaging in politics.</t>
-  </si>
-  <si>
-    <t>It's inspiring! It's great to see new voices and ideas. How do you think young people can make a difference?Have you engaged with any youth activism groups?</t>
-  </si>
-  <si>
-    <t>It's a positive development. It's encouraging to see young voices being heard. How can we continue to engage more people?Have you considered organizing events or workshops to encourage political participation?</t>
-  </si>
-  <si>
-    <t>That's fantastic! It's great to see the younger generation taking an interest in politics.Have you been following any inspiring young politicians or activists?</t>
-  </si>
-  <si>
-    <t>It's a positive trend! Yes, it's inspiring to see a more youthful interest in politics.How do you think we can continue encouraging young people to stay engaged?</t>
-  </si>
-  <si>
-    <t>It's great to see their enthusiasm. Yes, it's inspiring to witness their dedication. How do you think they can make a difference?Have you considered mentoring or supporting young political activists?</t>
+    <t>SFTANNO-000118-0004</t>
+  </si>
+  <si>
+    <t>We can support local community clinics and increase our involvement in community-based programs that advocate for health equity.</t>
+  </si>
+  <si>
+    <t>Yes, these initiatives are crucial in promoting health equity and ensuring that everyone has access to quality healthcare. It's surprising that we still have a long way to go in promoting health equity, but I'm hopeful that with continued efforts, we can achieve this goal.What other initiatives can we support to promote health equity?</t>
+  </si>
+  <si>
+    <t>That's a fantastic idea! It's great to see people coming together to make a positive impact on the healthcare system. It's surprising how much progress we can make when we work together towards a common goal, and it's great to see people taking action to improve the healthcare system.How can we continue to work towards making healthcare more accessible and equitable for all?</t>
+  </si>
+  <si>
+    <t>That's a fantastic idea, and it's uplifting to know that we can make a difference in our own community. I'm surprised to learn that local community clinics can play a significant role in addressing healthcare disparities.How can we encourage more people to get involved and support these initiatives?</t>
+  </si>
+  <si>
+    <t>That's a fantastic idea! It's wonderful to see people taking an active role in promoting health equity. I'm genuinely surprised by your enthusiasm for this issue. It's inspiring to see someone taking action towards promoting health equity.What other ideas do you have to promote health equity at the local level?</t>
+  </si>
+  <si>
+    <t>That's a fantastic idea! We can work towards creating a more inclusive healthcare system by supporting these initiatives. It's surprising how much of a difference community-based programs can make in promoting health equity.What other initiatives can we take to support health equity in our communities?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -513,15 +518,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -559,7 +561,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -567,12 +569,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -876,14 +873,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.83203125" style="2" customWidth="1"/>
-    <col min="2" max="13" width="27.6640625" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9.1640625" style="2"/>
+    <col min="1" max="1" width="9.6640625" style="2" customWidth="1"/>
+    <col min="2" max="13" width="27.33203125" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -924,7 +921,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="115.2">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -935,18 +932,18 @@
         <v>15</v>
       </c>
       <c r="D2" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="2">
-        <v>3</v>
+      <c r="F2" s="3">
+        <v>2</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="3">
         <v>3</v>
       </c>
       <c r="I2" s="2" t="s">
@@ -958,11 +955,11 @@
       <c r="K2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="128" x14ac:dyDescent="0.2">
+      <c r="L2" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="172.8">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -972,35 +969,35 @@
       <c r="C3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="2">
-        <v>4</v>
+      <c r="D3" s="3">
+        <v>5</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="2">
-        <v>3</v>
+      <c r="F3" s="3">
+        <v>5</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="2">
-        <v>2</v>
+      <c r="H3" s="3">
+        <v>3</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="2">
-        <v>3</v>
+      <c r="J3" s="3">
+        <v>5</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="128" x14ac:dyDescent="0.2">
+      <c r="L3" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="129.6">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -1010,35 +1007,35 @@
       <c r="C4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="2">
-        <v>3</v>
+      <c r="F4" s="3">
+        <v>4</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="3">
         <v>4</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="3">
         <v>3</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+      <c r="L4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="100.8">
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
@@ -1048,35 +1045,35 @@
       <c r="C5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>3</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="3">
         <v>3</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="3">
         <v>3</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="2">
-        <v>4</v>
+      <c r="J5" s="3">
+        <v>3</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="112" x14ac:dyDescent="0.2">
+      <c r="L5" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="115.2">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
@@ -1086,35 +1083,35 @@
       <c r="C6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>3</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="2">
-        <v>3</v>
+      <c r="F6" s="3">
+        <v>4</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="2">
-        <v>3</v>
+      <c r="H6" s="3">
+        <v>4</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="3">
         <v>4</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L6" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+      <c r="L6" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="115.2">
       <c r="A7" s="2" t="s">
         <v>48</v>
       </c>
@@ -1124,35 +1121,35 @@
       <c r="C7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="2">
-        <v>2</v>
+      <c r="D7" s="3">
+        <v>4</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="2">
-        <v>4</v>
+      <c r="F7" s="3">
+        <v>3</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="2">
-        <v>2</v>
+      <c r="H7" s="3">
+        <v>3</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="J7" s="2">
-        <v>2</v>
+      <c r="J7" s="3">
+        <v>4</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="112" x14ac:dyDescent="0.2">
+      <c r="L7" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="129.6">
       <c r="A8" s="2" t="s">
         <v>55</v>
       </c>
@@ -1162,35 +1159,35 @@
       <c r="C8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="3">
         <v>3</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="2">
-        <v>3</v>
+      <c r="F8" s="3">
+        <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="2">
-        <v>3</v>
+      <c r="H8" s="3">
+        <v>4</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="J8" s="2">
-        <v>3</v>
+      <c r="J8" s="3">
+        <v>4</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="L8" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="112" x14ac:dyDescent="0.2">
+      <c r="L8" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="100.8">
       <c r="A9" s="2" t="s">
         <v>62</v>
       </c>
@@ -1200,35 +1197,35 @@
       <c r="C9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="3">
         <v>4</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="2">
-        <v>3</v>
+      <c r="F9" s="3">
+        <v>5</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="3">
         <v>3</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="J9" s="2">
-        <v>3</v>
+      <c r="J9" s="3">
+        <v>2</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="L9" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="176" x14ac:dyDescent="0.2">
+      <c r="L9" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="115.2">
       <c r="A10" s="2" t="s">
         <v>69</v>
       </c>
@@ -1238,35 +1235,35 @@
       <c r="C10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="2">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>4</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="3">
         <v>3</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="3">
         <v>3</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J10" s="2">
-        <v>3</v>
+      <c r="J10" s="3">
+        <v>4</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="L10" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="144" x14ac:dyDescent="0.2">
+      <c r="L10" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="100.8">
       <c r="A11" s="2" t="s">
         <v>76</v>
       </c>
@@ -1276,35 +1273,35 @@
       <c r="C11" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="3">
         <v>3</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F11" s="2">
-        <v>2</v>
+      <c r="F11" s="3">
+        <v>4</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="H11" s="2">
-        <v>3</v>
+      <c r="H11" s="3">
+        <v>4</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J11" s="2">
-        <v>3</v>
+      <c r="J11" s="3">
+        <v>4</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="L11" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="144" x14ac:dyDescent="0.2">
+      <c r="L11" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="187.2">
       <c r="A12" s="2" t="s">
         <v>83</v>
       </c>
@@ -1314,35 +1311,35 @@
       <c r="C12" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="2">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>5</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F12" s="2">
-        <v>1</v>
+      <c r="F12" s="3">
+        <v>4</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H12" s="2">
-        <v>4</v>
+      <c r="H12" s="3">
+        <v>5</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="J12" s="2">
-        <v>4</v>
+      <c r="J12" s="3">
+        <v>3</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="L12" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+      <c r="L12" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="129.6">
       <c r="A13" s="2" t="s">
         <v>90</v>
       </c>
@@ -1352,35 +1349,35 @@
       <c r="C13" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="3">
         <v>3</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="2">
-        <v>3</v>
+      <c r="F13" s="3">
+        <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="H13" s="2">
-        <v>3</v>
+      <c r="H13" s="3">
+        <v>2</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="J13" s="2">
-        <v>3</v>
+      <c r="J13" s="3">
+        <v>4</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="L13" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="129.6">
       <c r="A14" s="2" t="s">
         <v>97</v>
       </c>
@@ -1390,35 +1387,35 @@
       <c r="C14" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D14" s="2">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="3">
         <v>4</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="3">
         <v>3</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="J14" s="2">
-        <v>3</v>
+      <c r="J14" s="3">
+        <v>5</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="L14" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="112" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="144">
       <c r="A15" s="2" t="s">
         <v>104</v>
       </c>
@@ -1428,35 +1425,35 @@
       <c r="C15" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D15" s="2">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>5</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="3">
         <v>4</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="3">
         <v>3</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="J15" s="2">
-        <v>2</v>
+      <c r="J15" s="3">
+        <v>5</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="L15" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="112" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="158.4">
       <c r="A16" s="2" t="s">
         <v>111</v>
       </c>
@@ -1466,35 +1463,35 @@
       <c r="C16" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="3">
         <v>4</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="3">
         <v>3</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="3">
         <v>3</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="J16" s="2">
-        <v>2</v>
+      <c r="J16" s="3">
+        <v>3</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="L16" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="112" x14ac:dyDescent="0.2">
+      <c r="L16" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="100.8">
       <c r="A17" s="2" t="s">
         <v>118</v>
       </c>
@@ -1504,35 +1501,35 @@
       <c r="C17" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="2">
-        <v>4</v>
+      <c r="D17" s="3">
+        <v>1</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="F17" s="2">
-        <v>3</v>
+      <c r="F17" s="3">
+        <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="H17" s="2">
-        <v>3</v>
+      <c r="H17" s="3">
+        <v>4</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="J17" s="2">
-        <v>3</v>
+      <c r="J17" s="3">
+        <v>2</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="L17" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="144" x14ac:dyDescent="0.2">
+      <c r="L17" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="86.4">
       <c r="A18" s="2" t="s">
         <v>125</v>
       </c>
@@ -1542,35 +1539,35 @@
       <c r="C18" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D18" s="2">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>5</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F18" s="2">
-        <v>4</v>
+      <c r="F18" s="3">
+        <v>5</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="H18" s="2">
-        <v>3</v>
+      <c r="H18" s="3">
+        <v>5</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="J18" s="2">
-        <v>4</v>
+      <c r="J18" s="3">
+        <v>5</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="L18" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="112" x14ac:dyDescent="0.2">
+      <c r="L18" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="144">
       <c r="A19" s="2" t="s">
         <v>132</v>
       </c>
@@ -1580,35 +1577,35 @@
       <c r="C19" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D19" s="2">
-        <v>3</v>
+      <c r="D19" s="3">
+        <v>5</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="F19" s="2">
-        <v>2</v>
+      <c r="F19" s="3">
+        <v>3</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H19" s="2">
-        <v>3</v>
+      <c r="H19" s="3">
+        <v>2</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="3">
         <v>3</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="L19" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="128" x14ac:dyDescent="0.2">
+      <c r="L19" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="115.2">
       <c r="A20" s="2" t="s">
         <v>139</v>
       </c>
@@ -1618,35 +1615,35 @@
       <c r="C20" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D20" s="2">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>5</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F20" s="2">
-        <v>2</v>
+      <c r="F20" s="3">
+        <v>3</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="H20" s="2">
-        <v>2</v>
+      <c r="H20" s="3">
+        <v>5</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="J20" s="2">
-        <v>3</v>
+      <c r="J20" s="3">
+        <v>4</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="L20" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="128" x14ac:dyDescent="0.2">
+      <c r="L20" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="129.6">
       <c r="A21" s="2" t="s">
         <v>146</v>
       </c>
@@ -1656,35 +1653,35 @@
       <c r="C21" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="3">
         <v>4</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F21" s="2">
-        <v>2</v>
+      <c r="F21" s="3">
+        <v>5</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="H21" s="2">
-        <v>3</v>
+      <c r="H21" s="3">
+        <v>4</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="J21" s="2">
-        <v>3</v>
+      <c r="J21" s="3">
+        <v>5</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L21" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="112" x14ac:dyDescent="0.2">
+      <c r="L21" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="201.6">
       <c r="A22" s="2" t="s">
         <v>153</v>
       </c>
@@ -1694,37 +1691,37 @@
       <c r="C22" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D22" s="2">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>1</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="3">
         <v>4</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="H22" s="2">
-        <v>3</v>
+      <c r="H22" s="3">
+        <v>4</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="J22" s="2">
-        <v>2</v>
+      <c r="J22" s="3">
+        <v>4</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="L22" s="2">
-        <v>3</v>
+      <c r="L22" s="3">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22 F2:F22 H2:H22 J2:J22 L2:L22" xr:uid="{35EB2117-EE87-419E-8A42-58C31378F635}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22 F2:F22 H2:H22 J2:J22 L2:L22" xr:uid="{D9236AEB-EC7E-4A66-A53B-F7A681D09AD0}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
